--- a/output/pdf_financials_xlsx/DBG.xlsx
+++ b/output/pdf_financials_xlsx/DBG.xlsx
@@ -1347,40 +1347,40 @@
         <v>-0.810571</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.675118</v>
+        <v>-0.675118</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.996559</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.79526</v>
+        <v>-0.79526</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.365244</v>
+        <v>-0.365244</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.990658</v>
+        <v>-0.990658</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2.657162</v>
+        <v>-2.127398</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.08363</v>
+        <v>-1.613394</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3.533044</v>
+        <v>-3.533044</v>
       </c>
     </row>
     <row r="17">
@@ -1667,40 +1667,40 @@
         <v>-0.810571</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.675118</v>
+        <v>-0.675118</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.996559</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.79526</v>
+        <v>-0.79526</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.365244</v>
+        <v>-0.365244</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.990658</v>
+        <v>-0.990658</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>2.39228</v>
+        <v>-2.39228</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.348512</v>
+        <v>-1.348512</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3.533044</v>
+        <v>-3.533044</v>
       </c>
     </row>
     <row r="21">
@@ -1856,40 +1856,40 @@
         <v>-0.810571</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.675118</v>
+        <v>-0.675118</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.996559</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.79526</v>
+        <v>-0.79526</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.365244</v>
+        <v>-0.365244</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.990658</v>
+        <v>-0.990658</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2.39228</v>
+        <v>-2.39228</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.348512</v>
+        <v>-1.348512</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3.533044</v>
+        <v>-3.533044</v>
       </c>
     </row>
     <row r="24">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>119.614</v>
+        <v>-119.614</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>176.6522</v>
+        <v>-176.6522</v>
       </c>
     </row>
     <row r="27">
@@ -2132,40 +2132,40 @@
         <v>-0.810571</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.675118</v>
+        <v>-0.675118</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.996559</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.79526</v>
+        <v>-0.79526</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.365244</v>
+        <v>-0.365244</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.990658</v>
+        <v>-0.990658</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>2.657162</v>
+        <v>-2.127398</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.08363</v>
+        <v>-1.613394</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>3.533044</v>
+        <v>-3.533044</v>
       </c>
     </row>
     <row r="28">
@@ -2258,40 +2258,40 @@
         <v>-0.810571</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.675118</v>
+        <v>-0.675118</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.996559</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.79526</v>
+        <v>-0.79526</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.365244</v>
+        <v>-0.365244</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.990658</v>
+        <v>-0.990658</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.657162</v>
+        <v>-2.127398</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.08363</v>
+        <v>-1.613394</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>3.533044</v>
+        <v>-3.533044</v>
       </c>
     </row>
     <row r="30">
@@ -2418,40 +2418,40 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>9.968605602518778</v>
+        <v>-12.45098472406198</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>24.4439522715318</v>
+        <v>-16.41768842576581</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6310,49 +6310,49 @@
         <v>0.1177</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.156032</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.172159</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.435112</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.7688739999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.108513</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.22423</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.227755</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.810163</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.095813</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.65816</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.491982</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.332258</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.406206</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>8.027563000000001</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>11.995314</v>
       </c>
     </row>
     <row r="93">
@@ -10632,7 +10632,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12390,7 +12394,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13518,7 +13526,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -16360,7 +16372,11 @@
           <t>Share based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -17096,7 +17112,11 @@
           <t>Share‐based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -19384,7 +19404,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -20654,7 +20678,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -44598,10 +44626,10 @@
         </is>
       </c>
       <c r="U341" s="5" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="V341" s="5" t="n">
-        <v>3.533044</v>
+        <v>-3.533044</v>
       </c>
     </row>
     <row r="342">
@@ -46362,31 +46390,31 @@
         </is>
       </c>
       <c r="M359" s="5" t="n">
-        <v>0.79526</v>
+        <v>-0.79526</v>
       </c>
       <c r="N359" s="5" t="n">
-        <v>0.365244</v>
+        <v>-0.365244</v>
       </c>
       <c r="O359" s="5" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="P359" s="5" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="Q359" s="5" t="n">
-        <v>0.990658</v>
+        <v>-0.990658</v>
       </c>
       <c r="R359" s="5" t="n">
-        <v>2.39228</v>
+        <v>-2.39228</v>
       </c>
       <c r="S359" s="5" t="n">
-        <v>1.348512</v>
+        <v>-1.348512</v>
       </c>
       <c r="T359" s="5" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="U359" s="5" t="n">
-        <v>1.844934</v>
+        <v>-1.844934</v>
       </c>
       <c r="V359" t="inlineStr">
         <is>
@@ -47816,10 +47844,10 @@
         </is>
       </c>
       <c r="S373" s="5" t="n">
-        <v>1.348512</v>
+        <v>-1.348512</v>
       </c>
       <c r="T373" s="5" t="n">
-        <v>1.624798</v>
+        <v>-1.624798</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -49948,10 +49976,10 @@
         </is>
       </c>
       <c r="O394" s="5" t="n">
-        <v>0.884421</v>
+        <v>-0.884421</v>
       </c>
       <c r="P394" s="5" t="n">
-        <v>0.398169</v>
+        <v>-0.398169</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -54244,10 +54272,10 @@
         </is>
       </c>
       <c r="K435" s="5" t="n">
-        <v>0.675118</v>
+        <v>-0.675118</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>0.996559</v>
+        <v>-0.996559</v>
       </c>
       <c r="M435" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DBG.xlsx
+++ b/output/pdf_financials_xlsx/DBG.xlsx
@@ -966,13 +966,13 @@
         <v>0.281129</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.314378</v>
+        <v>0.810571</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.135932</v>
+        <v>0.7865180000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.144662</v>
+        <v>0.6531130000000001</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.792863</v>
@@ -1029,13 +1029,13 @@
         <v>-0.281129</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.314378</v>
+        <v>-0.810571</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.135932</v>
+        <v>-0.7865180000000001</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.144662</v>
+        <v>-0.6531130000000001</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.792863</v>
@@ -1116,19 +1116,19 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003186</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.041052</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06457</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.055455</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.119733</v>
       </c>
     </row>
     <row r="13">
@@ -2153,19 +2153,19 @@
         <v>-0.990658</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.127398</v>
+        <v>-2.124212</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.613394</v>
+        <v>-1.572342</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.624798</v>
+        <v>-1.560228</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.844934</v>
+        <v>-1.789479</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-3.533044</v>
+        <v>-3.413311</v>
       </c>
     </row>
     <row r="28">
@@ -2279,19 +2279,19 @@
         <v>-0.990658</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.127398</v>
+        <v>-2.124212</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.613394</v>
+        <v>-1.572342</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.624798</v>
+        <v>-1.560228</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.844934</v>
+        <v>-1.789479</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-3.533044</v>
+        <v>-3.413311</v>
       </c>
     </row>
     <row r="30">
@@ -2570,25 +2570,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017894</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.463247</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.133405</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.186334</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.401088</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010501</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.373407</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.146743</v>
@@ -2696,25 +2696,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017894</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.463247</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.133405</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.186334</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.401088</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010501</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.373407</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.146743</v>
@@ -3452,25 +3452,25 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.017894</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.463247</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.133405</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.241334</v>
+        <v>0.055</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.451088</v>
+        <v>0.05</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.025501</v>
+        <v>0.015</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.373407</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.13815</v>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -44226,7 +44226,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -45946,7 +45946,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -54028,7 +54028,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
